--- a/src/attributions/attributions_ig_traj_298.xlsx
+++ b/src/attributions/attributions_ig_traj_298.xlsx
@@ -1002,19 +1002,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2170461487869008</v>
+        <v>0.3090452411823946</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.05975528358099093</v>
+        <v>0.06858197226475905</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2201138667216569</v>
+        <v>-0.2580937766420587</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -1023,55 +1023,55 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04624854970930557</v>
+        <v>0.09468232161605115</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.003803729843468771</v>
+        <v>-0.004537381423014021</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0054426775770867</v>
+        <v>0.005321822482219983</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0121931202114987</v>
+        <v>-0.1056316874383861</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0868252484346145</v>
+        <v>-0.08876752135260182</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.03073929221168106</v>
+        <v>-0.1179686885115422</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
@@ -1080,22 +1080,22 @@
         <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0382599538654256</v>
+        <v>0.1204909075576635</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1248757428227917</v>
+        <v>0.05574707491768357</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.05272487440239207</v>
+        <v>0.1426421313689668</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -1104,40 +1104,40 @@
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04727546788309357</v>
+        <v>0.1240628564336683</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.04069551459811029</v>
+        <v>-0.05468214925075224</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.1266174540529857</v>
+        <v>-0.2334080160793761</v>
       </c>
       <c r="AQ2" t="n">
         <v>-0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2648216490784184</v>
+        <v>0.6605533326792286</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1146,25 +1146,25 @@
         <v>-0</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.158183454195903</v>
+        <v>-0.2446433548197511</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.4032229626462012</v>
+        <v>-0.4145454973390755</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.1258434913437113</v>
+        <v>0.1155903603534005</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,13 +1173,13 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.0321798712052718</v>
+        <v>0.06354345695446442</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.07420996449020013</v>
+        <v>-0.1682280474042692</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
         <v>-0</v>
@@ -1191,73 +1191,73 @@
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.001813804961735719</v>
+        <v>0.07024336343322565</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.02494621923470392</v>
+        <v>0.08542670307367577</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.02298061902257294</v>
+        <v>0.1569639767492343</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.07039851144054037</v>
+        <v>0.2210686711751446</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.1132601381946213</v>
+        <v>-0.1019873709470566</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.1328434026368685</v>
+        <v>-0.2767261156106648</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
         <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1073822586619718</v>
+        <v>-0.2579791212192447</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.03080327952085105</v>
+        <v>-0.06246542476836745</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.1152601678946842</v>
+        <v>0.1771601283681623</v>
       </c>
       <c r="CJ2" t="n">
         <v>0</v>
@@ -1266,58 +1266,58 @@
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.004952620690293392</v>
+        <v>-0.2419717810089807</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
         <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.04683927353884149</v>
+        <v>0.05823623442732907</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.01088647837865527</v>
+        <v>0.1487782641373321</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.08796629451604106</v>
+        <v>-0.2459956557600103</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01803138483404039</v>
+        <v>-0.05932614306533676</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.1334773349378525</v>
+        <v>0.1517059269718812</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
@@ -1326,73 +1326,73 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.05390966898013396</v>
+        <v>-0.1304530710247239</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.03964686353397251</v>
+        <v>-0.05258112797751905</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.004301978598605613</v>
+        <v>0.1386717639002207</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.01465169216944954</v>
+        <v>-0.09144986067297706</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.1168675655337137</v>
+        <v>0.001259247068048539</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.01375070556506886</v>
+        <v>0.07686626210868473</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.05133033603566994</v>
+        <v>0.1531542436854383</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
         <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.01138238411469794</v>
+        <v>-0.04031904439138505</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.01486296360789663</v>
+        <v>0.1717622430373899</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1404,25 +1404,25 @@
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.1183834044830427</v>
+        <v>-0.1246728294020258</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.00657862766244103</v>
+        <v>-0.0876946304949535</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.124754724094843</v>
+        <v>0.15251226559154</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>-0</v>
@@ -1431,10 +1431,10 @@
         <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.04773220213343761</v>
+        <v>-0.1638853005417523</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
@@ -1443,37 +1443,37 @@
         <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.03458485190971846</v>
+        <v>-0.1924983131969843</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.05692480113302847</v>
+        <v>0.1655584447708482</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.08614608822317865</v>
+        <v>-0.2373045676457447</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.03335915137871331</v>
+        <v>-0.1187707585295715</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.1202570701488062</v>
+        <v>0.1607772201807394</v>
       </c>
       <c r="FD2" t="n">
         <v>0</v>
@@ -1485,85 +1485,85 @@
         <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.07584601399976601</v>
+        <v>-0.1282552618633541</v>
       </c>
       <c r="FI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ2" t="n">
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.06607827494170669</v>
+        <v>-0.06166041973372087</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.1369253727303383</v>
+        <v>0.2840597021542615</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.1581160502589445</v>
+        <v>-0.01354226086905758</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.05833573986616377</v>
+        <v>0.06358466761025044</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.08684198627359421</v>
+        <v>0.04977563576019872</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.04502832762619102</v>
+        <v>-0.1201723210806603</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
         <v>0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0.02892805697973632</v>
+        <v>0.1844128726722734</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06188241556675032</v>
+        <v>0.356990222936502</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,25 +2149,25 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.00919528496563511</v>
+        <v>0.0220525717311173</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.02096794634652264</v>
+        <v>-0.139113602231268</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01583180676886485</v>
+        <v>0.1384412850576173</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,40 +2176,40 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.003870392348116805</v>
+        <v>-0.02962947320802266</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01137817643241358</v>
+        <v>-0.08891539115063261</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00221558817205783</v>
+        <v>0.1285754117412413</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.004864649138517006</v>
+        <v>-0.1260306164882175</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001368053858590308</v>
+        <v>-0.03274342816722655</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>-0</v>
@@ -2221,79 +2221,79 @@
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0109584462755314</v>
+        <v>0.0282460201890781</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0228047992025442</v>
+        <v>-0.2331253679905819</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.0007665886333811035</v>
+        <v>0.03407016642560937</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.004387812711740875</v>
+        <v>0.1902961099298199</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01112489320974974</v>
+        <v>0.1350259023472225</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.01606030600129673</v>
+        <v>-0.1387497303333746</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.08283945622608539</v>
+        <v>0.7401460792974859</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.004261689772855511</v>
+        <v>-0.212844233455272</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.005681785358982464</v>
+        <v>-0.182845444988128</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02782589872503623</v>
+        <v>-0.02603101642158416</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,40 +2311,40 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.019549124877929</v>
+        <v>-0.06256612241091052</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.04848099779482846</v>
+        <v>-0.1058755028573734</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02899641128218291</v>
+        <v>0.04287204020722209</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02612550003476191</v>
+        <v>0.130246068827055</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.004639947585217081</v>
+        <v>0.1469991435735549</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,7 +2356,7 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02863953808049267</v>
+        <v>0.371863239996362</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,43 +2365,43 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.005118974974840005</v>
+        <v>-0.03343428744894922</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.004552350786474342</v>
+        <v>-0.2357657079612692</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>-0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.01841412203212578</v>
+        <v>-0.2366367439352777</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.002118904109182733</v>
+        <v>-0.02475558903598251</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.01906843224728092</v>
+        <v>0.1593026504163285</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
         <v>0</v>
@@ -2410,49 +2410,49 @@
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.00527981981179559</v>
+        <v>-0.1583482802732657</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
         <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.004108655922119841</v>
+        <v>0.08265434223804126</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0007809106633622541</v>
+        <v>-0.0005368565063359071</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT4" t="n">
         <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01412110748908113</v>
+        <v>-0.2141646274406068</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.003638293946648316</v>
+        <v>-0.02103884702721226</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.01873158737210883</v>
+        <v>0.1592680513527125</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2464,52 +2464,52 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.004318032461428666</v>
+        <v>-0.03500064536337061</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
         <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01812079702664662</v>
+        <v>-0.07243342027773597</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.003546490182692985</v>
+        <v>0.0381981839502944</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.005923831458935125</v>
+        <v>-0.1004499681973499</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-8.95803137745175e-05</v>
+        <v>0.005045798389804882</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.006199084901461501</v>
+        <v>0.01096105966138417</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>-0</v>
@@ -2518,46 +2518,46 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01775048927623112</v>
+        <v>0.08336716842357894</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.03205357836121387</v>
+        <v>-0.07633904146178534</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0005930411331872502</v>
+        <v>0.1252512036742044</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.01384135386648185</v>
+        <v>-0.04290063506293436</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.001024316817494005</v>
+        <v>-0.1298588274190507</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01136739744581012</v>
+        <v>0.08025539296084284</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
@@ -2569,10 +2569,10 @@
         <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.0151176610700421</v>
+        <v>-0.120314527228706</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
@@ -2581,37 +2581,37 @@
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.008658470596225855</v>
+        <v>-0.1981833145509987</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.004997676992950147</v>
+        <v>0.04087401940103448</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01643971944646957</v>
+        <v>-0.2354908320712711</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.004044660982815073</v>
+        <v>-0.06249427331599514</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.02020196961973531</v>
+        <v>0.1370694691002747</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
@@ -2620,13 +2620,13 @@
         <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.0001931502163546776</v>
+        <v>-0.2129666420269714</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,70 +2635,70 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02621339499649919</v>
+        <v>0.07817244621478675</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.01979613233959642</v>
+        <v>0.224937528140058</v>
       </c>
       <c r="FM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.001545785384382836</v>
+        <v>-0.02923275999523168</v>
       </c>
       <c r="FR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0004305234250826192</v>
+        <v>-0.0009684823460585909</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.008614041637559848</v>
+        <v>0.0984252938980041</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02722373650709928</v>
+        <v>-0.08883527549646714</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.006754551429212806</v>
+        <v>0.1032511967407685</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>0</v>
@@ -2709,22 +2709,22 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1219184922435678</v>
+        <v>0.3596587934806102</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.00341922424569569</v>
+        <v>0.04701253394394463</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.07554215579938897</v>
+        <v>-0.1737893151797207</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04787212156262561</v>
+        <v>0.1972385839958785</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,64 +2745,64 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.001065919297129571</v>
+        <v>-0.02050356167385696</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.04436512974791736</v>
+        <v>-0.1048566585218731</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.005346369061070973</v>
+        <v>0.1008062043297155</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01565563709737232</v>
+        <v>-0.1309635511870953</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.001837912597843148</v>
+        <v>-0.01664052696451674</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0198400566526704</v>
+        <v>0.04464816045266069</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02141697196959443</v>
+        <v>-0.2257415515704195</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.003131864756851275</v>
+        <v>-0.08593729336544681</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2817,22 +2817,22 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02090540267192832</v>
+        <v>0.1649419863892808</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.005648328108760059</v>
+        <v>0.1102783684175098</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.03744228037387603</v>
+        <v>-0.1054153519546961</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2841,22 +2841,22 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1430254650529754</v>
+        <v>0.6314944983237311</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001972021399295735</v>
+        <v>-0.1430461270688154</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.0804899250187244</v>
+        <v>-0.1939985228435721</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.05045559657957903</v>
+        <v>-0.00166960569581843</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,10 +2880,10 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.03946647271976187</v>
+        <v>-0.05358596249987858</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.07253849888305285</v>
+        <v>-0.1598287888623418</v>
       </c>
       <c r="BI5" t="n">
         <v>-0</v>
@@ -2892,28 +2892,28 @@
         <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03371498684132956</v>
+        <v>0.03597891687574522</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01956870652075751</v>
+        <v>0.07254997340886034</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.003965689451432413</v>
+        <v>0.04722070850917186</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>0</v>
@@ -2922,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.05116806930114831</v>
+        <v>0.308161113444726</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,13 +2934,13 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.001303406701031689</v>
+        <v>-0.02883878609189162</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.02388984077286906</v>
+        <v>-0.1354880624237273</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>-0</v>
@@ -2952,22 +2952,22 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.03740482327755392</v>
+        <v>-0.217174321146221</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.006396417242737202</v>
+        <v>-0.04840076487036296</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.03789734780422618</v>
+        <v>0.1321887507124207</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2979,49 +2979,49 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.006160283191042309</v>
+        <v>-0.1295911565612802</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0132598649037093</v>
+        <v>0.05421167611691716</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.002855032719408294</v>
+        <v>0.009374606953762575</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03239953157570981</v>
+        <v>-0.1940197640021956</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.0004151191401548538</v>
+        <v>-0.04769959422431577</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.04071832288578545</v>
+        <v>0.1356734250807938</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.009980225018701914</v>
+        <v>-0.05911762011671604</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.007550856845062566</v>
+        <v>-0.05057888358632381</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001557597627415997</v>
+        <v>0.03674997328495205</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.00469659320587397</v>
+        <v>-0.1073022857837814</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.003814337520042726</v>
+        <v>-0.001245428164752054</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.01283373467887755</v>
+        <v>0.08686405340242774</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,19 +3087,19 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.02192092560421685</v>
+        <v>0.02309928583987801</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03172828514516485</v>
+        <v>0.1047281624243083</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.003640348428581356</v>
+        <v>0.1229969291436613</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3108,28 +3108,28 @@
         <v>-0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0329163327992961</v>
+        <v>-0.05047978054719228</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.002021538045435149</v>
+        <v>-0.1002014461203396</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.02793303738141083</v>
+        <v>0.04271529679866341</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3138,64 +3138,64 @@
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0322274775026795</v>
+        <v>-0.1020339593147921</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.007628490835113849</v>
+        <v>-0.1000891848899627</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.02848116422246836</v>
+        <v>0.08794312527388219</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.03338839772884131</v>
+        <v>-0.2149313210351812</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.001829895696801994</v>
+        <v>-0.07378981977737391</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.03673689978036491</v>
+        <v>0.1200942846639016</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.008528316195541794</v>
+        <v>-0.2422941632775134</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,70 +3204,70 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02280911646014498</v>
+        <v>0.06524182636341437</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0214696168193547</v>
+        <v>0.2489491057001093</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.007765853870291177</v>
+        <v>-0.03214507368865865</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001764752710660483</v>
+        <v>-0.008439801244018977</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02597642590847323</v>
+        <v>0.1364030772445146</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02232209276413775</v>
+        <v>-0.05369989581638961</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.006911032116960865</v>
+        <v>0.009347113875979477</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3847,154 +3847,154 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2197667908849288</v>
+        <v>0.5578233739821539</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.06763846107580557</v>
+        <v>-0.002276327687486007</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04778675991960982</v>
+        <v>0.06526552827665759</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.06871271768981697</v>
+        <v>-0.2160888884973607</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1277587378901571</v>
+        <v>0.4993542099199259</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.05462433734185475</v>
+        <v>-0.1120233051405439</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02946027265860778</v>
+        <v>-0.04205129660193223</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.04317462987899704</v>
+        <v>-0.1126920379458048</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04937144377824131</v>
+        <v>0.1385991341198753</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01514882904960532</v>
+        <v>-0.1466654076126097</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02754256094888084</v>
+        <v>-0.1434895456064261</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02309280354320864</v>
+        <v>0.006694252528539393</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01840914406672245</v>
+        <v>0.1465613418905699</v>
       </c>
       <c r="AD7" t="n">
         <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.04367134585154401</v>
+        <v>-0.3394198412530866</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.00125026988709313</v>
+        <v>-0.2172587604576743</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0119005617031316</v>
+        <v>-0.1541780242071397</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.001656097944060184</v>
+        <v>0.2670730249954267</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.03113131002247291</v>
+        <v>-0.1450366566588353</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01359647667537389</v>
+        <v>0.1670010875248334</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.02883069633471027</v>
+        <v>-0.1910001426642614</v>
       </c>
       <c r="AQ7" t="n">
         <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.3244104642102168</v>
+        <v>0.8155728531843117</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.009397941958847021</v>
+        <v>-0.004228945384757997</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.04677756664568994</v>
+        <v>-0.1414491872986918</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.04363053488610782</v>
+        <v>-0.1224664155625487</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,58 +4003,58 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02025646108011033</v>
+        <v>0.01816792888228675</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.04292178833260405</v>
+        <v>-0.0916837570388969</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.09432179855542493</v>
+        <v>-0.1375731519483069</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.1236468880906035</v>
+        <v>-0.2544931411963827</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.07009425816355222</v>
+        <v>0.03899142412124584</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.04521396862708939</v>
+        <v>-0.002509924346538094</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.06597463524192362</v>
+        <v>0.1470223782879805</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01369774018282329</v>
+        <v>0.009761877696496859</v>
       </c>
       <c r="BR7" t="n">
         <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
         <v>0</v>
@@ -4063,19 +4063,19 @@
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1198428804506877</v>
+        <v>0.3776346301940939</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02495097964529424</v>
+        <v>-0.086450497649896</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.01273602252141491</v>
+        <v>-0.009874549155010388</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.02348861010011724</v>
+        <v>-0.1655355969374503</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4084,28 +4084,28 @@
         <v>-0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.05866956524858317</v>
+        <v>-0.2702416595451853</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.006510601720493901</v>
+        <v>0.04023978871117893</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.001319947976155638</v>
+        <v>-0.06583626314199072</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.04405373934626156</v>
+        <v>0.1165501145961387</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4114,301 +4114,301 @@
         <v>0</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02195677800762075</v>
+        <v>-0.1933365221164951</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.03441075806007817</v>
+        <v>0.139470317511012</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.01931733497489368</v>
+        <v>0.01906795409302841</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.0164019664527915</v>
+        <v>0.08857434423209844</v>
       </c>
       <c r="CS7" t="n">
         <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.05104901735226843</v>
+        <v>-0.2450263319433091</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.02359816977854992</v>
+        <v>0.04563486735221417</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.004730084119904106</v>
+        <v>-0.08257239161756685</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.05180191264958028</v>
+        <v>0.1122135875887873</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.01321611014989833</v>
+        <v>-0.048787806640476</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.07826675187084432</v>
+        <v>-0.02973966325784675</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.01561664936553353</v>
+        <v>0.4731048605914669</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.003009584250383389</v>
+        <v>0.02178720578549196</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.03798320532819007</v>
+        <v>-0.09494536045495842</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.02724777894867367</v>
+        <v>0.06337540368320493</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0227020118237608</v>
+        <v>-0.09776319057018079</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.02653254520503731</v>
+        <v>0.1543843604885614</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW7" t="n">
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.006054731141806383</v>
+        <v>0.1476123856479851</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.002795734057268609</v>
+        <v>0.07060383409165563</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.03584555947100912</v>
+        <v>0.01682263222457325</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.00258541826303072</v>
+        <v>-0.01521958738026408</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.08593620734471746</v>
+        <v>-0.114526649424992</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.03471547948101402</v>
+        <v>0.07162425893107426</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0367353333852423</v>
+        <v>-0.1009926891466333</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.008353643140979465</v>
+        <v>-0.02670890678746801</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03584935300058535</v>
+        <v>-0.09565654023149291</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0003255704418690113</v>
+        <v>-0.08395119485912086</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.004785980301531378</v>
+        <v>-0.07426719753134392</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.06831097152479307</v>
+        <v>0.2493991858716779</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.04709916610512214</v>
+        <v>-0.2822239029585729</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.00705408079461627</v>
+        <v>0.0427143634043378</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01414332293081877</v>
+        <v>-0.1164456146798406</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.04210197371695123</v>
+        <v>0.08940379044054639</v>
       </c>
       <c r="FD7" t="n">
         <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.03531574651317242</v>
+        <v>-0.2221661969964162</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.03391435740103591</v>
+        <v>0.1418176003039721</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.003532563844474296</v>
+        <v>-0.03954314121581561</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.00800320829410152</v>
+        <v>0.3488679216806419</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.006610866519397472</v>
+        <v>-0.1847785072457316</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.01631024947911528</v>
+        <v>0.2851599745447508</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.006098666960557544</v>
+        <v>0.006130310389735823</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0003246674849548178</v>
+        <v>0.08912753497891127</v>
       </c>
       <c r="FV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW7" t="n">
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03548492396418154</v>
+        <v>-0.09927253597834998</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.02308780334112119</v>
+        <v>-0.194549181245576</v>
       </c>
       <c r="GC7" t="n">
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.001559574311184672</v>
+        <v>-0.08116691836157176</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4982,10 +4982,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.6333321328806398</v>
+        <v>-0.2084792159555122</v>
       </c>
       <c r="C9" t="n">
         <v>-0</v>
@@ -4994,13 +4994,13 @@
         <v>-0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1440645318562985</v>
+        <v>-0.006384425030151558</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9478170162920985</v>
+        <v>0.189834941200862</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5009,10 +5009,10 @@
         <v>-0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2768047235892421</v>
+        <v>-0.1096166751430972</v>
       </c>
       <c r="L9" t="n">
         <v>-0</v>
@@ -5021,10 +5021,10 @@
         <v>-0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04714759552105241</v>
+        <v>0.04994366285250167</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6130080528745286</v>
+        <v>0.1275513823510485</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5039,22 +5039,22 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.08987364958049784</v>
+        <v>-0.07447894772877092</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
         <v>-0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09929075318987055</v>
+        <v>-0.01028612858590421</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01322540642381054</v>
+        <v>-0.03034365880860297</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.2292662844646398</v>
+        <v>0.04934224178435086</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
@@ -5075,10 +5075,10 @@
         <v>-0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.009041921356546138</v>
+        <v>0.1325664531607018</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.1794684588853131</v>
+        <v>0.02895627485620352</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
@@ -5093,22 +5093,22 @@
         <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.1023697505229313</v>
+        <v>-0.1064408785403294</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.133995609998641</v>
+        <v>-0.06988470441452106</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.2848560101649846</v>
+        <v>0.1473352732760574</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.3965576578619361</v>
+        <v>-0.2712167576070214</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -5129,25 +5129,25 @@
         <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.3715169595648701</v>
+        <v>0.08545254241921577</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.898446928044848</v>
+        <v>0.1229258411756775</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.407520166372013</v>
+        <v>0.08502860584449448</v>
       </c>
       <c r="BE9" t="n">
         <v>-0</v>
@@ -5156,25 +5156,25 @@
         <v>-0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.1853226290135963</v>
+        <v>0.1992327461192683</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.1937053163495445</v>
+        <v>0.1106634423137898</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.1100656542514048</v>
+        <v>0.01639344190314307</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
@@ -5183,10 +5183,10 @@
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.1007975938249138</v>
+        <v>-0.05520747974159876</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.003827582056926658</v>
+        <v>-0.04510861521099055</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
@@ -5201,25 +5201,25 @@
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.2135037216207077</v>
+        <v>-0.2043496119656293</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
         <v>-0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.1011905607977777</v>
+        <v>0.004108661655667133</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.3343115544923815</v>
+        <v>0.08431087855857648</v>
       </c>
       <c r="CA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.1917405269793536</v>
+        <v>0.1225254342914704</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01392885338782887</v>
+        <v>-0.01319583423710121</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0.1923463616915325</v>
+        <v>-0.07743273012909681</v>
       </c>
       <c r="CJ9" t="n">
         <v>0</v>
@@ -5249,28 +5249,28 @@
         <v>-0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
         <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.01870983651228235</v>
+        <v>0.0735202445044103</v>
       </c>
       <c r="CO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP9" t="n">
         <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.2128664555115923</v>
+        <v>-0.1443724349365737</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.1178104982967436</v>
+        <v>-0.04107696025664406</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
         <v>0</v>
@@ -5279,10 +5279,10 @@
         <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.1588111466996637</v>
+        <v>0.1107408049406598</v>
       </c>
       <c r="CX9" t="n">
         <v>-0</v>
@@ -5291,10 +5291,10 @@
         <v>-0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.06267377383661794</v>
+        <v>-0.01041636696222213</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0.2316167622665714</v>
+        <v>-0.06522510937247344</v>
       </c>
       <c r="DB9" t="n">
         <v>-0</v>
@@ -5309,52 +5309,52 @@
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01400185717823196</v>
+        <v>-0.003995657365040254</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
         <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.2584495789923995</v>
+        <v>0.0498187860226145</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.03326402031973864</v>
+        <v>-0.01065246494434375</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.1236803356152932</v>
+        <v>0.02124188153493036</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.1041139570545863</v>
+        <v>0.007669797168659903</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.06952409350688951</v>
+        <v>-0.02506587373349488</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.1309708494361494</v>
+        <v>-0.03391614190114071</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -5372,10 +5372,10 @@
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.2929865533099328</v>
+        <v>0.0497579787310474</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.1000511045917228</v>
+        <v>0.02212487484629061</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
@@ -5384,25 +5384,25 @@
         <v>-0</v>
       </c>
       <c r="EE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0793975541923761</v>
+        <v>0.05819865071308115</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.1459935794740662</v>
+        <v>0.01846939864496878</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0.1644080759119566</v>
+        <v>-0.01011193822996479</v>
       </c>
       <c r="EL9" t="n">
         <v>0</v>
@@ -5411,13 +5411,13 @@
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.1711079067931622</v>
+        <v>0.09367782183312537</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
@@ -5426,25 +5426,25 @@
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.08809072694169402</v>
+        <v>0.07162776965567434</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.006277793455702759</v>
+        <v>0.09626699634157608</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.178110070323006</v>
+        <v>0.1272744353608633</v>
       </c>
       <c r="EZ9" t="n">
         <v>0</v>
@@ -5453,13 +5453,13 @@
         <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.05886863043145255</v>
+        <v>-0.003162623344727291</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0.2320116557213362</v>
+        <v>-0.06032154245826478</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>-0</v>
@@ -5468,10 +5468,10 @@
         <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.01800079849460328</v>
+        <v>0.1259115030178628</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
@@ -5480,37 +5480,37 @@
         <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.01501975987369351</v>
+        <v>-0.04267275441389723</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0.2392463723158225</v>
+        <v>-0.0993115145385092</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.008423739451268418</v>
+        <v>0.1100794135240663</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
         <v>0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.1484080108072988</v>
+        <v>-0.01005489410683047</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0.3303382599966145</v>
+        <v>-0.07058023032862215</v>
       </c>
       <c r="FV9" t="n">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         <v>-0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.1283005601406513</v>
+        <v>0.113629337868941</v>
       </c>
       <c r="GA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB9" t="n">
         <v>0</v>
@@ -5537,7 +5537,7 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0872130603933849</v>
+        <v>0.03830205089082456</v>
       </c>
       <c r="GE9" t="n">
         <v>0</v>
@@ -5551,22 +5551,22 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1333747704097537</v>
+        <v>0.5148325973131788</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.006346353310403234</v>
+        <v>0.0002700440850149603</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.09238705329937291</v>
+        <v>-0.280564342159551</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
@@ -5578,10 +5578,10 @@
         <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1074339899046069</v>
+        <v>0.6075606347199339</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,16 +5590,16 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.004922750975620268</v>
+        <v>-0.1269468041886106</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.06333348995726427</v>
+        <v>-0.1982353532227623</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
@@ -5608,7 +5608,7 @@
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.007850565653307266</v>
+        <v>0.1139995950450614</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,16 +5617,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01521090670274852</v>
+        <v>-0.004443227824983744</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.01571716032506547</v>
+        <v>-0.1177768790472474</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -5635,19 +5635,19 @@
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.008316099349665495</v>
+        <v>0.03215875159809943</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01235721675422421</v>
+        <v>-0.06130712917934466</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01731685655992342</v>
+        <v>0.07795744972795222</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -5662,22 +5662,22 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.006742006836319209</v>
+        <v>0.1657124953135528</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.008719181063579343</v>
+        <v>0.06451357517745945</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.04350250535089837</v>
+        <v>-0.09482639186049169</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,37 +5686,37 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1091571088354197</v>
+        <v>0.7338388647635505</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.00885172471062848</v>
+        <v>-0.2759153201846885</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.06423155134413359</v>
+        <v>-0.3212020212138874</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
         <v>-0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.05188276019307981</v>
+        <v>-0.1839698045602423</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,10 +5725,10 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.02485971350127424</v>
+        <v>0.01335580953829206</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.05555194651347658</v>
+        <v>-0.0419011910793562</v>
       </c>
       <c r="BI10" t="n">
         <v>-0</v>
@@ -5737,52 +5737,52 @@
         <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.03996804065148661</v>
+        <v>0.009174731277238977</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.01419698175298306</v>
+        <v>0.089843474575002</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01794783304865634</v>
+        <v>0.04391066948069087</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.05605944782850338</v>
+        <v>0.4384048668309342</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.002626131867736737</v>
+        <v>-0.03677873754959628</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.02406693501916508</v>
+        <v>-0.1703999915772176</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5797,25 +5797,25 @@
         <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.02983591228312463</v>
+        <v>-0.2394700460300695</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.00271046045514352</v>
+        <v>0.017515858575498</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02423289219041722</v>
+        <v>0.1075699391986752</v>
       </c>
       <c r="CJ10" t="n">
         <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL10" t="n">
         <v>0</v>
@@ -5824,61 +5824,61 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.008574699962323611</v>
+        <v>-0.09829052415643967</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.00351575685253533</v>
+        <v>0.07772980135248647</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.008853434160957165</v>
+        <v>0.04492254828031166</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.0223002523975217</v>
+        <v>-0.2237061299253223</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.0022845470218262</v>
+        <v>0.01441453771117305</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.02978972586931386</v>
+        <v>0.1233328294515248</v>
       </c>
       <c r="DB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.004042153493190569</v>
+        <v>0.01108555135666103</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
@@ -5887,10 +5887,10 @@
         <v>-0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.008102356115746018</v>
+        <v>0.02229123519137749</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0126818434258586</v>
+        <v>0.09452965097261611</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
@@ -5902,28 +5902,28 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.0117108452349807</v>
+        <v>-0.08465824679981289</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.007697112199631012</v>
+        <v>-0.0183323931389147</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.004775339957483572</v>
+        <v>0.08594244480854549</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,46 +5932,46 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.03625581567067365</v>
+        <v>-0.1572603468630954</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.009218750434680942</v>
+        <v>0.06259317427101001</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.01784494534518465</v>
+        <v>-0.1024368562931136</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02071768898491964</v>
+        <v>-0.1283539480535044</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.003104876901817064</v>
+        <v>-0.05031721999726278</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0156409895730309</v>
+        <v>0.0412747467355729</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
@@ -5986,19 +5986,19 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.007571463270012959</v>
+        <v>0.0938704795640192</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.003932367996226053</v>
+        <v>0.0142643575323563</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.001880821807891714</v>
+        <v>-0.04128950148844369</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
@@ -6007,52 +6007,52 @@
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
         <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.02198731072545749</v>
+        <v>-0.2578804784633106</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.001206428374172076</v>
+        <v>-0.007625591026963668</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.03021805443850384</v>
+        <v>0.1250087453308819</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.003380217103684103</v>
+        <v>-0.1260089855804763</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.01607362177234817</v>
+        <v>-0.01451814246354441</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.02992896954521935</v>
+        <v>0.1362518640586858</v>
       </c>
       <c r="FM10" t="n">
         <v>-0</v>
@@ -6067,7 +6067,7 @@
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.0196555951489811</v>
+        <v>-0.2368096317537156</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,37 +6076,37 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.02443977178562185</v>
+        <v>-0.06122378289717301</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.0008763209283351258</v>
+        <v>-0.0101744704646738</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01311891922634132</v>
+        <v>-0.1134967812113027</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.02613882249697758</v>
+        <v>0.07198302679113594</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,16 +6123,16 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.3595239659945326</v>
+        <v>-0.3737637328004914</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1918948061953517</v>
+        <v>0.1326478602353585</v>
       </c>
       <c r="E11" t="n">
-        <v>0.217961686878524</v>
+        <v>0.07984689236739811</v>
       </c>
       <c r="F11" t="n">
         <v>-0</v>
@@ -6144,25 +6144,25 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.290603672443886</v>
+        <v>-0.4559974253514154</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2105292914795927</v>
+        <v>0.223032096262105</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2389788726610567</v>
+        <v>0.1539367503506809</v>
       </c>
       <c r="O11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -6177,25 +6177,25 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1015994294792082</v>
+        <v>-0.0402388324492669</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01694052201451101</v>
+        <v>0.01267256161566748</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.04183647001244236</v>
+        <v>-0.005544661424828436</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>-0</v>
@@ -6204,22 +6204,22 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.1524543817303817</v>
+        <v>-0.01986218768638529</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.05730643156480612</v>
+        <v>0.1338706937573633</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.03112473842292171</v>
+        <v>-0.2222037577602377</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -6228,76 +6228,76 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.03530618224662264</v>
+        <v>-0.1467362683141169</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.04496369266459647</v>
+        <v>0.03771858075953894</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.07773047799036843</v>
+        <v>-0.2313778420852493</v>
       </c>
       <c r="AP11" t="n">
         <v>-0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.2823760744888923</v>
+        <v>-0.2428530737293749</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.009386233642463646</v>
+        <v>0.140834232216819</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.01912585227520819</v>
+        <v>0.02256290232743481</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.01270378074326078</v>
+        <v>0.05066757266978159</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.1947370835745189</v>
+        <v>0.01267303549555298</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.2801864307627785</v>
+        <v>0.131204742198662</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
@@ -6312,16 +6312,16 @@
         <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.09746939744970234</v>
+        <v>0.1121550478169164</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0.03966367599017617</v>
+        <v>0.08290456634644046</v>
       </c>
       <c r="BP11" t="n">
-        <v>-0.1006469971429728</v>
+        <v>0.001854649371135884</v>
       </c>
       <c r="BQ11" t="n">
         <v>0</v>
@@ -6339,25 +6339,25 @@
         <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>-0.2214552231237848</v>
+        <v>-0.1967383025962886</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.001954980983664282</v>
+        <v>0.06910249671461589</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.04295490695730891</v>
+        <v>-0.0085159241749709</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC11" t="n">
         <v>-0</v>
@@ -6366,25 +6366,25 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.09111559250187642</v>
+        <v>0.1941410410625169</v>
       </c>
       <c r="CF11" t="n">
         <v>0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0.04630099311145542</v>
+        <v>-0.05770707510185234</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.002501104486842532</v>
+        <v>-0.004755495526076575</v>
       </c>
       <c r="CI11" t="n">
         <v>0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
         <v>0</v>
@@ -6393,19 +6393,19 @@
         <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.03036194770759994</v>
+        <v>0.089814116304601</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.06177633397348618</v>
+        <v>-0.08566313376769037</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.08264093758651204</v>
+        <v>-0.03688885645439984</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS11" t="n">
         <v>0</v>
@@ -6420,22 +6420,22 @@
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.08768772856841285</v>
+        <v>0.203680935099142</v>
       </c>
       <c r="CX11" t="n">
         <v>-0</v>
       </c>
       <c r="CY11" t="n">
-        <v>-0.06427216599515229</v>
+        <v>-0.05883352196937213</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.003251567564702623</v>
+        <v>-0.03258943965871855</v>
       </c>
       <c r="DA11" t="n">
         <v>-0</v>
       </c>
       <c r="DB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6447,52 +6447,52 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.1674791704590838</v>
+        <v>0.1516227042501961</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0.05120534549396998</v>
+        <v>-0.02342471104732869</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0.008569236863323306</v>
+        <v>-0.000970404644517681</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL11" t="n">
         <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0444027720261606</v>
+        <v>0.09032915425264003</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.03951346969164644</v>
+        <v>-0.04203099856430466</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.06924336164510286</v>
+        <v>0.02707078849941816</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
       </c>
       <c r="DU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV11" t="n">
         <v>-0</v>
@@ -6501,22 +6501,22 @@
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1020258637098203</v>
+        <v>0.04218837314236253</v>
       </c>
       <c r="DY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.09150862549650279</v>
+        <v>0.04949671606083903</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.05065278254419057</v>
+        <v>0.006867971764129158</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
         <v>-0</v>
@@ -6528,22 +6528,22 @@
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.05382829121024003</v>
+        <v>0.2267285513372236</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0.04169300521635982</v>
+        <v>-0.0568662035802833</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.1036737619249987</v>
+        <v>-0.03789969876844101</v>
       </c>
       <c r="EK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM11" t="n">
         <v>0</v>
@@ -6552,28 +6552,28 @@
         <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0004639062558998706</v>
+        <v>-0.1168263580159574</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.03281302057021471</v>
+        <v>-0.01012929929656321</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.02831961310528018</v>
+        <v>0.004782772460820705</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
@@ -6582,16 +6582,16 @@
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.09068410370469708</v>
+        <v>0.2302553806432373</v>
       </c>
       <c r="EZ11" t="n">
         <v>0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-0.05954802278726774</v>
+        <v>-0.0707934113191805</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.005773934316406578</v>
+        <v>-0.0006280483128592738</v>
       </c>
       <c r="FC11" t="n">
         <v>0</v>
@@ -6600,52 +6600,52 @@
         <v>-0</v>
       </c>
       <c r="FE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG11" t="n">
         <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.05169731641457217</v>
+        <v>0.08428186888562736</v>
       </c>
       <c r="FI11" t="n">
         <v>0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.08810583646586569</v>
+        <v>0.1085450814762721</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.04179208425015184</v>
+        <v>0.03676015370198812</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.02522769737549652</v>
+        <v>0.1785516605937419</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.03322027598198776</v>
+        <v>0.01260390136827294</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.009205554983633504</v>
+        <v>-0.05637390529607172</v>
       </c>
       <c r="FU11" t="n">
         <v>0</v>
@@ -6654,37 +6654,37 @@
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
         <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.05225639164725931</v>
+        <v>0.2022148667834</v>
       </c>
       <c r="GA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.06616922842704878</v>
+        <v>-0.001531745628289719</v>
       </c>
       <c r="GC11" t="n">
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4870340664615532</v>
+        <v>0.3451182324101872</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,16 +6701,16 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1171038079518017</v>
+        <v>-0.02415007276200525</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4436249964418046</v>
+        <v>-0.1423975481477552</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4564442769178869</v>
+        <v>0.4556398729406052</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,25 +6728,25 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05570592675916219</v>
+        <v>-0.1057542333602102</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4518573142021146</v>
+        <v>-0.2037387679502438</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03678668043720053</v>
+        <v>0.0994621737550056</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -6755,16 +6755,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.08439262822239568</v>
+        <v>-0.1181451646230026</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.01567068857811676</v>
+        <v>-0.01165391202914747</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,19 +6773,19 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.02363507836424826</v>
+        <v>-0.03181093238320283</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.01012467495818293</v>
+        <v>-0.2802260515972894</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.03447034086699631</v>
+        <v>-0.0004806981102348303</v>
       </c>
       <c r="AH12" t="n">
         <v>-0</v>
@@ -6800,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.08346482370634739</v>
+        <v>0.03391320067782991</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
@@ -6809,10 +6809,10 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.001425139274130004</v>
+        <v>-0.04382687751844315</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.08288815890890448</v>
+        <v>0.01800998439388342</v>
       </c>
       <c r="AQ12" t="n">
         <v>-0</v>
@@ -6824,10 +6824,10 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4142823062989933</v>
+        <v>0.490930550772916</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,16 +6836,16 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.07056162875261536</v>
+        <v>-0.2412630341333792</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.2195072107427806</v>
+        <v>-0.1060183635823349</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
@@ -6854,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1084983479853896</v>
+        <v>-0.03244371999040717</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,52 +6863,52 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1511296373082835</v>
+        <v>-0.01743696709524062</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.1920463743209763</v>
+        <v>-0.08854328880803962</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1430673738132707</v>
+        <v>0.0555858806580355</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.003506804419984493</v>
+        <v>0.08095184223925117</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.01774829638850664</v>
+        <v>-0.0353695774531211</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2174578064331273</v>
+        <v>0.2645884054932645</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.07027843473932166</v>
+        <v>-0.07607225122038919</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.1317131469424722</v>
+        <v>-0.1065766498934343</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6935,22 +6935,22 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.08493679991571336</v>
+        <v>-0.1128628071677499</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.005132296706541574</v>
+        <v>0.02940671068759908</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.107260316561954</v>
+        <v>0.05005876308788209</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,100 +6962,100 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.411111576022698e-05</v>
+        <v>-0.1176648399683078</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.01656313510158922</v>
+        <v>0.0987659328249483</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.02173635870421967</v>
+        <v>0.09696302121904032</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.06794519309467903</v>
+        <v>-0.1132667735478171</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.002517826506811512</v>
+        <v>0.008266387471978583</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.1129463761574095</v>
+        <v>0.07134993351079165</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.04002326517017469</v>
+        <v>-0.04182103570936625</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0444566794875837</v>
+        <v>-0.1773522024170269</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0.001614683906987056</v>
+        <v>0.05430905562071246</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.006081052987154392</v>
+        <v>-0.006789881564130029</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.03351720870604942</v>
+        <v>-0.06165173203514228</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0.00651404814989466</v>
+        <v>0.07945600496514979</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7064,13 +7064,13 @@
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.05777594466092893</v>
+        <v>-0.0203989119697206</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
@@ -7079,106 +7079,106 @@
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01639577769065341</v>
+        <v>-0.0676568575607339</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.05440360332127209</v>
+        <v>0.03633715307927934</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.09693440032671177</v>
+        <v>-0.04598912915854268</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.02439302318152298</v>
+        <v>0.02204225341916105</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.1195640580710318</v>
+        <v>-0.009853383573066175</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.02990216264525762</v>
+        <v>-0.005227696832770167</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.01296633880913288</v>
+        <v>-0.01220162516658875</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.07094629067274934</v>
+        <v>0.1364584260180013</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.06543195927951648</v>
+        <v>-0.130932432158351</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.006229404879093165</v>
+        <v>-0.002061555924192711</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.1024537790435004</v>
+        <v>0.03987951912620769</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.002535719417640378</v>
+        <v>0.2075057372435904</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,16 +7187,16 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.008508884200727705</v>
+        <v>-0.08888362194263089</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.05172385674770193</v>
+        <v>0.1169911234280748</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
@@ -7205,46 +7205,46 @@
         <v>0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.004963051982165477</v>
+        <v>0.01095474566180105</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.008810654514323803</v>
+        <v>-0.02433236845990461</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.03438754936987051</v>
+        <v>-0.04959525460895942</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.04462418624405818</v>
+        <v>-0.0392241248176862</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.05108333755087999</v>
+        <v>0.06229019800014492</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1555227955103367</v>
+        <v>0.3740873085411197</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,25 +8408,25 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08280241633837762</v>
+        <v>-0.01212069175337799</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07228254118439849</v>
+        <v>-0.1420221622722794</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1280013609926359</v>
+        <v>0.4550155857997566</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,25 +8435,25 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05768573777505789</v>
+        <v>-0.1030346101625517</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.07598714090533507</v>
+        <v>-0.1872297503630286</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01378244307605709</v>
+        <v>0.08850790259557874</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -8462,40 +8462,40 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.004451178988662641</v>
+        <v>-0.08737791763617689</v>
       </c>
       <c r="X15" t="n">
-        <v>0.009296517155136153</v>
+        <v>-0.01195679459117023</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.004937052603166965</v>
+        <v>-0.03445648712941773</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.01397086337945391</v>
+        <v>-0.2456376296061947</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01246458326384953</v>
+        <v>0.01208147322881906</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
@@ -8507,22 +8507,22 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01048426267962558</v>
+        <v>0.03864887039576933</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.008843058167262783</v>
+        <v>-0.03478953138166604</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.01472490147678882</v>
+        <v>0.004348853773135694</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,28 +8531,28 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1072825700670186</v>
+        <v>0.4082565567656767</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.02880010261672456</v>
+        <v>-0.2569226983256364</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.02119212093019258</v>
+        <v>-0.1019174011449789</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
@@ -8561,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.03149636970574076</v>
+        <v>-0.007966828915457077</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,52 +8570,52 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.05775229627875221</v>
+        <v>0.003299825105484479</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.05909104473704765</v>
+        <v>-0.06672767056896817</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.03556435611813727</v>
+        <v>0.03790515352353375</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0160377211932141</v>
+        <v>0.05412149956945281</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01704690532514525</v>
+        <v>-0.02904912448350688</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.05103091105067987</v>
+        <v>0.2284431608214726</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
@@ -8624,10 +8624,10 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.01218046926464564</v>
+        <v>-0.06484531704446789</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0.01384008897907786</v>
+        <v>-0.108101791999787</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
@@ -8636,31 +8636,31 @@
         <v>-0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.02622308846222178</v>
+        <v>-0.106248834828522</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.007127736093176795</v>
+        <v>0.02637823890535754</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.01772200217820961</v>
+        <v>0.05235108424751526</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -8669,52 +8669,52 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0008607606247808709</v>
+        <v>-0.1167963372686887</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.007075855757484145</v>
+        <v>0.1418910920064637</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.01179765717120735</v>
+        <v>0.06948314519810558</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.01997228527183853</v>
+        <v>-0.1042914444843911</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.006098553888960175</v>
+        <v>0.01336787605902164</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01817422480022265</v>
+        <v>0.07393732256271993</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>0</v>
@@ -8723,22 +8723,22 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.03236358042313904</v>
+        <v>-0.07613463879940778</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.05139714038333401</v>
+        <v>-0.2088158290936235</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.01369322867674388</v>
+        <v>0.0664830782668345</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
@@ -8747,28 +8747,28 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.005787316285419271</v>
+        <v>-0.01453139399809695</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01937102480609069</v>
+        <v>-0.04380413370108927</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.009748317299426336</v>
+        <v>0.04598420032442908</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
@@ -8777,49 +8777,49 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.02951577427682513</v>
+        <v>-0.008128724834928856</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01498315768491325</v>
+        <v>-0.05739258479727879</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.01825960522851271</v>
+        <v>0.02186635189298738</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.0315053328593496</v>
+        <v>-0.04910027289638845</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.00944317674849344</v>
+        <v>0.009966225733988959</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.01334605781814872</v>
+        <v>-0.0008290111176221996</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
@@ -8828,82 +8828,82 @@
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.01243019102766987</v>
+        <v>-0.03263751016830274</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.002243096035829807</v>
+        <v>-0.01666909488296208</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.01165242559899074</v>
+        <v>0.1081606505080878</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.0208915055260241</v>
+        <v>-0.1236182570442468</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.009264301360075101</v>
+        <v>0.001119420975175839</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.02170654796978215</v>
+        <v>0.04480882699908054</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.01511337365004362</v>
+        <v>0.1682489665630392</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0113268961668335</v>
+        <v>-0.08182097191585727</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01985781488408164</v>
+        <v>0.1168730928665216</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
@@ -8912,63 +8912,63 @@
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>7.644719732458803e-05</v>
+        <v>0.001766033095943371</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.001509859052916248</v>
+        <v>-0.008890543018079875</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.01880918805336776</v>
+        <v>-0.02826654740530361</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.001820653164314721</v>
+        <v>-0.03526500023485375</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
         <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.005457780234660795</v>
+        <v>0.06675703004937075</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.1266462604957166</v>
+        <v>0.2568294364946774</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0359596502453245</v>
+        <v>0.08360029537802897</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1458807809284861</v>
+        <v>-0.1124021230301778</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8989,10 +8989,10 @@
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1005695273084039</v>
+        <v>0.2217196001047798</v>
       </c>
       <c r="K16" t="n">
         <v>-0</v>
@@ -9001,43 +9001,43 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.002737779122467324</v>
+        <v>-0.007165351043765546</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0997243053547566</v>
+        <v>-0.1079803910484537</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>-0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01760666690443216</v>
+        <v>-0.06928175277144705</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.03898100455986269</v>
+        <v>-0.04621480493013201</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.02367567826519899</v>
+        <v>-0.08056909819103956</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.01516222809156062</v>
+        <v>0.0545615304003013</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -9055,43 +9055,43 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.02746700724001907</v>
+        <v>-0.03953367418522752</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.02875747820365326</v>
+        <v>0.05219803461472458</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.02170311454758471</v>
+        <v>0.01635961694893267</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.007094937415410008</v>
+        <v>0.0310684134670413</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01299687962429524</v>
+        <v>0.01725490832228489</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -9100,25 +9100,25 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.08472652476482592</v>
+        <v>-0.0180578642833223</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.1007914678233191</v>
+        <v>0.08887558904301493</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.08600565149370705</v>
+        <v>-0.007113253437926324</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
         <v>0</v>
@@ -9127,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.01499549256361632</v>
+        <v>0.1617831854512066</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.01190784752073141</v>
+        <v>-0.02019540684000256</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.04702454220862393</v>
+        <v>0.002295561210419389</v>
       </c>
       <c r="BI16" t="n">
         <v>0</v>
@@ -9154,10 +9154,10 @@
         <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.007487808577764449</v>
+        <v>-0.06679451029213296</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
@@ -9166,37 +9166,37 @@
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.003610416424803363</v>
+        <v>-0.1113391538630767</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.008104688305153049</v>
+        <v>0.03653506681344443</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.03643594286452657</v>
+        <v>-0.02642080760106553</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.03598242985426318</v>
+        <v>-0.0702652693062062</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.06421245250715174</v>
+        <v>-0.1104025499013803</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9205,10 +9205,10 @@
         <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-0.02249073403637856</v>
+        <v>-0.06422544393623388</v>
       </c>
       <c r="CE16" t="n">
         <v>0</v>
@@ -9220,13 +9220,13 @@
         <v>0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.01066464430794283</v>
+        <v>0.007021126430780321</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.04343561869056956</v>
+        <v>0.03115380220022167</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9235,25 +9235,25 @@
         <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.004126862283695319</v>
+        <v>0.01181028276288585</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.06820944344543946</v>
+        <v>0.08373939567032432</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.001346799260798693</v>
+        <v>-0.04380478783386278</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
         <v>-0</v>
@@ -9262,7 +9262,7 @@
         <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0.02108001772460196</v>
+        <v>-0.06726026660128644</v>
       </c>
       <c r="CW16" t="n">
         <v>-0</v>
@@ -9274,40 +9274,40 @@
         <v>-0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.01460815439289092</v>
+        <v>0.004563328884568592</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03937246904179714</v>
+        <v>0.03598994833441783</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0.0001534932277220459</v>
+        <v>-0.005146031250466448</v>
       </c>
       <c r="DF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.03079357996395915</v>
+        <v>-0.06032322361351384</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.001550474019576347</v>
+        <v>0.01431398112090277</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
         <v>0</v>
@@ -9316,7 +9316,7 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0.0005372762060466832</v>
+        <v>-0.03987372890085466</v>
       </c>
       <c r="DO16" t="n">
         <v>0</v>
@@ -9325,13 +9325,13 @@
         <v>0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.03730876190525402</v>
+        <v>-0.05332094162376333</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.01723860783134225</v>
+        <v>0.08169112504517606</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9340,37 +9340,37 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>-0.008746059748456648</v>
+        <v>0.02465871043844876</v>
       </c>
       <c r="DX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY16" t="n">
         <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01650795672862657</v>
+        <v>0.1237911810008313</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.03860945368572078</v>
+        <v>0.06352424167544639</v>
       </c>
       <c r="EC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE16" t="n">
         <v>0</v>
       </c>
       <c r="EF16" t="n">
-        <v>-0.02203262574153988</v>
+        <v>0.003466002153019663</v>
       </c>
       <c r="EG16" t="n">
         <v>0</v>
@@ -9382,22 +9382,22 @@
         <v>0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>-0.003408451035381646</v>
+        <v>-0.02625681375732344</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.04728923408716374</v>
+        <v>0.0510532135942809</v>
       </c>
       <c r="EL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>-0.01277627041603102</v>
+        <v>-0.03844273207820576</v>
       </c>
       <c r="EP16" t="n">
         <v>0</v>
@@ -9406,13 +9406,13 @@
         <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.02803751493072065</v>
+        <v>0.006067814825159359</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.002817743768328517</v>
+        <v>0.04406886628997701</v>
       </c>
       <c r="EU16" t="n">
         <v>0</v>
@@ -9424,7 +9424,7 @@
         <v>-0</v>
       </c>
       <c r="EX16" t="n">
-        <v>-0.01808398236400945</v>
+        <v>-0.05967497713790787</v>
       </c>
       <c r="EY16" t="n">
         <v>0</v>
@@ -9436,22 +9436,22 @@
         <v>0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.02408577528846209</v>
+        <v>-0.006747037493913817</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.04115578127544132</v>
+        <v>0.04533085295682484</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.007376195651755181</v>
+        <v>0.127769368547643</v>
       </c>
       <c r="FH16" t="n">
         <v>-0</v>
@@ -9460,13 +9460,13 @@
         <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.01202097803954294</v>
+        <v>-5.861337664423544e-05</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0.002121784118489793</v>
+        <v>0.1059281336776556</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
@@ -9478,10 +9478,10 @@
         <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0006546982649096399</v>
+        <v>0.003074093359563177</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,13 +9490,13 @@
         <v>0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.0006216824476783274</v>
+        <v>0.001590208613466223</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.01139849522618542</v>
+        <v>0.04096364891334509</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
         <v>-0</v>
@@ -9505,28 +9505,28 @@
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.00460258118434362</v>
+        <v>0.0725763631748053</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.01054367872908787</v>
+        <v>0.07896609230274053</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
         <v>0</v>
